--- a/backtest_runs/20260410_193731/by_symbol/UBL/UBL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/UBL/UBL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-1579.929999999996</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>98420.07000000001</v>
@@ -633,7 +633,7 @@
         <v>-3951.179999999996</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>95341.50999999999</v>
@@ -679,7 +679,7 @@
         <v>-10880.65000000001</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>84460.85999999999</v>
@@ -771,7 +771,7 @@
         <v>-1929.520000000001</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>87991.99000000001</v>
@@ -817,7 +817,7 @@
         <v>-2479.649999999994</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>85512.34000000001</v>
@@ -909,7 +909,7 @@
         <v>-3501.320000000004</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>83677.67</v>
@@ -1047,7 +1047,7 @@
         <v>-3617.849999999991</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>86460.84000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-7162.530000000002</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>80731.89999999999</v>
@@ -1231,7 +1231,7 @@
         <v>-848.2299999999988</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>79883.67</v>
@@ -1277,7 +1277,7 @@
         <v>-2070.439999999996</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>77813.23000000001</v>
@@ -1323,7 +1323,7 @@
         <v>-1317.060000000004</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>76496.17</v>
@@ -1415,7 +1415,7 @@
         <v>-3371.239999999999</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>78845.74000000001</v>
@@ -1461,7 +1461,7 @@
         <v>-3756.060000000004</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>75089.67999999999</v>
@@ -1507,7 +1507,7 @@
         <v>-5598.859999999991</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>69490.82000000001</v>
